--- a/Experiment Results for Equal Sets with Symmetric Distances/Experiment Summary for Equal Sets with Symmetric Distances.xlsx
+++ b/Experiment Results for Equal Sets with Symmetric Distances/Experiment Summary for Equal Sets with Symmetric Distances.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,741 +543,5181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>48.170166015625</v>
+        <v>393.737060546875</v>
       </c>
       <c r="F2" t="n">
-        <v>238698</v>
+        <v>643936</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.18017578125</v>
+        <v>0.93408203125</v>
       </c>
       <c r="I2" t="n">
-        <v>253675</v>
+        <v>680465</v>
       </c>
       <c r="J2" t="n">
-        <v>6.27</v>
+        <v>5.67</v>
       </c>
       <c r="K2" t="n">
-        <v>2.951171875</v>
+        <v>150.6171875</v>
       </c>
       <c r="L2" t="n">
-        <v>246986</v>
+        <v>650645</v>
       </c>
       <c r="M2" t="n">
-        <v>3.47</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3002.194091796875</v>
+        <v>15653.94995117188</v>
       </c>
       <c r="O2" t="n">
-        <v>259471</v>
+        <v>680998</v>
       </c>
       <c r="P2" t="n">
-        <v>8.699999999999999</v>
+        <v>5.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.479248046875</v>
+        <v>5.7412109375</v>
       </c>
       <c r="R2" t="n">
-        <v>259471</v>
+        <v>680998</v>
       </c>
       <c r="S2" t="n">
-        <v>8.699999999999999</v>
+        <v>5.76</v>
       </c>
       <c r="T2" t="n">
-        <v>2332.253173828125</v>
+        <v>25111.50122070312</v>
       </c>
       <c r="U2" t="n">
-        <v>259471</v>
+        <v>680998</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>47.481201171875</v>
+        <v>323.2939453125</v>
       </c>
       <c r="F3" t="n">
-        <v>226962</v>
+        <v>634357</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.18896484375</v>
+        <v>1.003173828125</v>
       </c>
       <c r="I3" t="n">
-        <v>235808</v>
+        <v>659872</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="K3" t="n">
-        <v>3.658935546875</v>
+        <v>134.127197265625</v>
       </c>
       <c r="L3" t="n">
-        <v>227738</v>
+        <v>637813</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
       <c r="N3" t="n">
-        <v>3052.229248046875</v>
+        <v>16008.28295898438</v>
       </c>
       <c r="O3" t="n">
-        <v>241132</v>
+        <v>660210</v>
       </c>
       <c r="P3" t="n">
-        <v>6.24</v>
+        <v>4.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.495849609375</v>
+        <v>6.151123046875</v>
       </c>
       <c r="R3" t="n">
-        <v>241132</v>
+        <v>660210</v>
       </c>
       <c r="S3" t="n">
-        <v>6.24</v>
+        <v>4.08</v>
       </c>
       <c r="T3" t="n">
-        <v>2343.873046875</v>
+        <v>25008.19799804688</v>
       </c>
       <c r="U3" t="n">
-        <v>241132</v>
+        <v>660210</v>
       </c>
       <c r="V3" t="n">
-        <v>6.24</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>125.672119140625</v>
+        <v>700.0341796875</v>
       </c>
       <c r="F4" t="n">
-        <v>235029</v>
+        <v>637183</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.18408203125</v>
+        <v>0.933837890625</v>
       </c>
       <c r="I4" t="n">
-        <v>243180</v>
+        <v>657968</v>
       </c>
       <c r="J4" t="n">
-        <v>3.47</v>
+        <v>3.26</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2802734375</v>
+        <v>142.990234375</v>
       </c>
       <c r="L4" t="n">
-        <v>238126</v>
+        <v>644040</v>
       </c>
       <c r="M4" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3005.696044921875</v>
+        <v>15657.52270507812</v>
       </c>
       <c r="O4" t="n">
-        <v>243180</v>
+        <v>657968</v>
       </c>
       <c r="P4" t="n">
-        <v>3.47</v>
+        <v>3.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5517578125</v>
+        <v>5.8369140625</v>
       </c>
       <c r="R4" t="n">
-        <v>243180</v>
+        <v>657968</v>
       </c>
       <c r="S4" t="n">
-        <v>3.47</v>
+        <v>3.26</v>
       </c>
       <c r="T4" t="n">
-        <v>2346.7568359375</v>
+        <v>25009.708984375</v>
       </c>
       <c r="U4" t="n">
-        <v>243180</v>
+        <v>657968</v>
       </c>
       <c r="V4" t="n">
-        <v>3.47</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>65.598876953125</v>
+        <v>389.46875</v>
       </c>
       <c r="F5" t="n">
-        <v>230743</v>
+        <v>637723</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.186767578125</v>
+        <v>0.933349609375</v>
       </c>
       <c r="I5" t="n">
-        <v>244134</v>
+        <v>677705</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8</v>
+        <v>6.27</v>
       </c>
       <c r="K5" t="n">
-        <v>6.323974609375</v>
+        <v>145.0908203125</v>
       </c>
       <c r="L5" t="n">
-        <v>232731</v>
+        <v>648887</v>
       </c>
       <c r="M5" t="n">
-        <v>0.86</v>
+        <v>1.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3264.43505859375</v>
+        <v>15696.17407226562</v>
       </c>
       <c r="O5" t="n">
-        <v>244706</v>
+        <v>664656</v>
       </c>
       <c r="P5" t="n">
-        <v>6.05</v>
+        <v>4.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55078125</v>
+        <v>5.674072265625</v>
       </c>
       <c r="R5" t="n">
-        <v>244706</v>
+        <v>664656</v>
       </c>
       <c r="S5" t="n">
-        <v>6.05</v>
+        <v>4.22</v>
       </c>
       <c r="T5" t="n">
-        <v>2339.994140625</v>
+        <v>25154.087890625</v>
       </c>
       <c r="U5" t="n">
-        <v>244706</v>
+        <v>664656</v>
       </c>
       <c r="V5" t="n">
-        <v>6.05</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>68.005126953125</v>
+        <v>562.33984375</v>
       </c>
       <c r="F6" t="n">
-        <v>237497</v>
+        <v>639088</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.18701171875</v>
+        <v>0.9208984375</v>
       </c>
       <c r="I6" t="n">
-        <v>250750</v>
+        <v>674574</v>
       </c>
       <c r="J6" t="n">
-        <v>5.58</v>
+        <v>5.55</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9541015625</v>
+        <v>231.419189453125</v>
       </c>
       <c r="L6" t="n">
-        <v>238986</v>
+        <v>642935</v>
       </c>
       <c r="M6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="N6" t="n">
-        <v>3027.083984375</v>
+        <v>15774.86889648438</v>
       </c>
       <c r="O6" t="n">
-        <v>250750</v>
+        <v>668218</v>
       </c>
       <c r="P6" t="n">
-        <v>5.58</v>
+        <v>4.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.549072265625</v>
+        <v>5.7412109375</v>
       </c>
       <c r="R6" t="n">
-        <v>250750</v>
+        <v>668218</v>
       </c>
       <c r="S6" t="n">
-        <v>5.58</v>
+        <v>4.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2352.02587890625</v>
+        <v>25152.43115234375</v>
       </c>
       <c r="U6" t="n">
-        <v>250750</v>
+        <v>668218</v>
       </c>
       <c r="V6" t="n">
-        <v>5.58</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>67.410888671875</v>
+        <v>328.529052734375</v>
       </c>
       <c r="F7" t="n">
-        <v>229708</v>
+        <v>628825</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.18115234375</v>
+        <v>1.02099609375</v>
       </c>
       <c r="I7" t="n">
-        <v>235344</v>
+        <v>655390</v>
       </c>
       <c r="J7" t="n">
-        <v>2.45</v>
+        <v>4.22</v>
       </c>
       <c r="K7" t="n">
-        <v>5.845947265625</v>
+        <v>164.502685546875</v>
       </c>
       <c r="L7" t="n">
-        <v>229961</v>
+        <v>638608</v>
       </c>
       <c r="M7" t="n">
-        <v>0.11</v>
+        <v>1.56</v>
       </c>
       <c r="N7" t="n">
-        <v>3010.961181640625</v>
+        <v>15758.53076171875</v>
       </c>
       <c r="O7" t="n">
-        <v>235344</v>
+        <v>661963</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>5.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.482177734375</v>
+        <v>6.0908203125</v>
       </c>
       <c r="R7" t="n">
-        <v>235344</v>
+        <v>661963</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>5.27</v>
       </c>
       <c r="T7" t="n">
-        <v>2345.351318359375</v>
+        <v>25097.09301757812</v>
       </c>
       <c r="U7" t="n">
-        <v>235344</v>
+        <v>661963</v>
       </c>
       <c r="V7" t="n">
-        <v>2.45</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>276.48291015625</v>
+        <v>399.965087890625</v>
       </c>
       <c r="F8" t="n">
-        <v>240328</v>
+        <v>640501</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.187255859375</v>
+        <v>0.951904296875</v>
       </c>
       <c r="I8" t="n">
-        <v>250810</v>
+        <v>666423</v>
       </c>
       <c r="J8" t="n">
-        <v>4.36</v>
+        <v>4.05</v>
       </c>
       <c r="K8" t="n">
-        <v>9.521240234375</v>
+        <v>152.552978515625</v>
       </c>
       <c r="L8" t="n">
-        <v>240328</v>
+        <v>644524</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="N8" t="n">
-        <v>3124.100830078125</v>
+        <v>15626.61181640625</v>
       </c>
       <c r="O8" t="n">
-        <v>250810</v>
+        <v>662929</v>
       </c>
       <c r="P8" t="n">
-        <v>4.36</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68115234375</v>
+        <v>5.8349609375</v>
       </c>
       <c r="R8" t="n">
-        <v>250810</v>
+        <v>662929</v>
       </c>
       <c r="S8" t="n">
-        <v>4.36</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2344.3662109375</v>
+        <v>25128.28198242188</v>
       </c>
       <c r="U8" t="n">
-        <v>250810</v>
+        <v>662929</v>
       </c>
       <c r="V8" t="n">
-        <v>4.36</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>48.883056640625</v>
+        <v>356.818115234375</v>
       </c>
       <c r="F9" t="n">
-        <v>232731</v>
+        <v>639938</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.189208984375</v>
+        <v>0.931884765625</v>
       </c>
       <c r="I9" t="n">
-        <v>242983</v>
+        <v>671599</v>
       </c>
       <c r="J9" t="n">
-        <v>4.41</v>
+        <v>4.95</v>
       </c>
       <c r="K9" t="n">
-        <v>2.951904296875</v>
+        <v>87.1640625</v>
       </c>
       <c r="L9" t="n">
-        <v>235263</v>
+        <v>647149</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>3017.31298828125</v>
+        <v>15655.6689453125</v>
       </c>
       <c r="O9" t="n">
-        <v>242983</v>
+        <v>667525</v>
       </c>
       <c r="P9" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5380859375</v>
+        <v>5.739013671875</v>
       </c>
       <c r="R9" t="n">
-        <v>242983</v>
+        <v>667525</v>
       </c>
       <c r="S9" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2343.779052734375</v>
+        <v>24928.048828125</v>
       </c>
       <c r="U9" t="n">
-        <v>242983</v>
+        <v>667525</v>
       </c>
       <c r="V9" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>125.88720703125</v>
+        <v>414.31591796875</v>
       </c>
       <c r="F10" t="n">
-        <v>243354</v>
+        <v>637152</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.187744140625</v>
+        <v>0.9208984375</v>
       </c>
       <c r="I10" t="n">
-        <v>258318</v>
+        <v>668249</v>
       </c>
       <c r="J10" t="n">
-        <v>6.15</v>
+        <v>4.88</v>
       </c>
       <c r="K10" t="n">
-        <v>5.872802734375</v>
+        <v>255.361083984375</v>
       </c>
       <c r="L10" t="n">
-        <v>243561</v>
+        <v>641361</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09</v>
+        <v>0.66</v>
       </c>
       <c r="N10" t="n">
-        <v>3030.552978515625</v>
+        <v>15542.18212890625</v>
       </c>
       <c r="O10" t="n">
-        <v>258318</v>
+        <v>670025</v>
       </c>
       <c r="P10" t="n">
-        <v>6.15</v>
+        <v>5.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.618896484375</v>
+        <v>5.84423828125</v>
       </c>
       <c r="R10" t="n">
-        <v>258318</v>
+        <v>670025</v>
       </c>
       <c r="S10" t="n">
-        <v>6.15</v>
+        <v>5.16</v>
       </c>
       <c r="T10" t="n">
-        <v>2338.057861328125</v>
+        <v>24998.78686523437</v>
       </c>
       <c r="U10" t="n">
-        <v>258318</v>
+        <v>670025</v>
       </c>
       <c r="V10" t="n">
-        <v>6.15</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1x2x5</t>
+          <t>1x2x15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1x2x5 : 2x5</t>
+          <t>1x2x15 : 2x15</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
+        <v>392.9208984375</v>
+      </c>
+      <c r="F11" t="n">
+        <v>632267</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.915283203125</v>
+      </c>
+      <c r="I11" t="n">
+        <v>654353</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K11" t="n">
+        <v>55.552978515625</v>
+      </c>
+      <c r="L11" t="n">
+        <v>637212</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15601.4521484375</v>
+      </c>
+      <c r="O11" t="n">
+        <v>662094</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.655029296875</v>
+      </c>
+      <c r="R11" t="n">
+        <v>662094</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="T11" t="n">
+        <v>24947.51000976562</v>
+      </c>
+      <c r="U11" t="n">
+        <v>662094</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>237.52685546875</v>
+      </c>
+      <c r="F12" t="n">
+        <v>446012</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.509765625</v>
+      </c>
+      <c r="I12" t="n">
+        <v>477727</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>43.793212890625</v>
+      </c>
+      <c r="L12" t="n">
+        <v>446808</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8424.986083984375</v>
+      </c>
+      <c r="O12" t="n">
+        <v>475757</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.271240234375</v>
+      </c>
+      <c r="R12" t="n">
+        <v>475757</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10698.96606445312</v>
+      </c>
+      <c r="U12" t="n">
+        <v>475757</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>813.254638671875</v>
+      </c>
+      <c r="F13" t="n">
+        <v>435755</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.491943359375</v>
+      </c>
+      <c r="I13" t="n">
+        <v>467694</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="K13" t="n">
+        <v>29.33984375</v>
+      </c>
+      <c r="L13" t="n">
+        <v>441033</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8492.48828125</v>
+      </c>
+      <c r="O13" t="n">
+        <v>462740</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.740234375</v>
+      </c>
+      <c r="R13" t="n">
+        <v>462740</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10638.43896484375</v>
+      </c>
+      <c r="U13" t="n">
+        <v>462740</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>307.110107421875</v>
+      </c>
+      <c r="F14" t="n">
+        <v>443227</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.48876953125</v>
+      </c>
+      <c r="I14" t="n">
+        <v>470477</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>43.739013671875</v>
+      </c>
+      <c r="L14" t="n">
+        <v>447149</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8450.700927734375</v>
+      </c>
+      <c r="O14" t="n">
+        <v>470477</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.27587890625</v>
+      </c>
+      <c r="R14" t="n">
+        <v>470477</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10594.203125</v>
+      </c>
+      <c r="U14" t="n">
+        <v>470477</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>204.029052734375</v>
+      </c>
+      <c r="F15" t="n">
+        <v>438578</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.48291015625</v>
+      </c>
+      <c r="I15" t="n">
+        <v>453294</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K15" t="n">
+        <v>18.177734375</v>
+      </c>
+      <c r="L15" t="n">
+        <v>447711</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8492.126953125</v>
+      </c>
+      <c r="O15" t="n">
+        <v>461818</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.339111328125</v>
+      </c>
+      <c r="R15" t="n">
+        <v>461818</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10696.19409179688</v>
+      </c>
+      <c r="U15" t="n">
+        <v>461818</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>206.730224609375</v>
+      </c>
+      <c r="F16" t="n">
+        <v>430798</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.561767578125</v>
+      </c>
+      <c r="I16" t="n">
+        <v>454607</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="K16" t="n">
+        <v>40.428955078125</v>
+      </c>
+      <c r="L16" t="n">
+        <v>438510</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8499.399169921875</v>
+      </c>
+      <c r="O16" t="n">
+        <v>454607</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.2509765625</v>
+      </c>
+      <c r="R16" t="n">
+        <v>454607</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10682.2998046875</v>
+      </c>
+      <c r="U16" t="n">
+        <v>454607</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>230.27978515625</v>
+      </c>
+      <c r="F17" t="n">
+        <v>438334</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.494873046875</v>
+      </c>
+      <c r="I17" t="n">
+        <v>473261</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="K17" t="n">
+        <v>47.4501953125</v>
+      </c>
+      <c r="L17" t="n">
+        <v>447439</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8457.98681640625</v>
+      </c>
+      <c r="O17" t="n">
+        <v>464677</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.2470703125</v>
+      </c>
+      <c r="R17" t="n">
+        <v>464677</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10651.17529296875</v>
+      </c>
+      <c r="U17" t="n">
+        <v>464677</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>262.790771484375</v>
+      </c>
+      <c r="F18" t="n">
+        <v>444392</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5009765625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>478002</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.402099609375</v>
+      </c>
+      <c r="L18" t="n">
+        <v>449752</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8474.3564453125</v>
+      </c>
+      <c r="O18" t="n">
+        <v>458372</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.662109375</v>
+      </c>
+      <c r="R18" t="n">
+        <v>458372</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10680.8759765625</v>
+      </c>
+      <c r="U18" t="n">
+        <v>458372</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>227.896240234375</v>
+      </c>
+      <c r="F19" t="n">
+        <v>433777</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.50927734375</v>
+      </c>
+      <c r="I19" t="n">
+        <v>463828</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="K19" t="n">
+        <v>37.158935546875</v>
+      </c>
+      <c r="L19" t="n">
+        <v>440695</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8466.4052734375</v>
+      </c>
+      <c r="O19" t="n">
+        <v>449791</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.34130859375</v>
+      </c>
+      <c r="R19" t="n">
+        <v>449791</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10623.2939453125</v>
+      </c>
+      <c r="U19" t="n">
+        <v>449791</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>155.52685546875</v>
+      </c>
+      <c r="F20" t="n">
+        <v>434110</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.48876953125</v>
+      </c>
+      <c r="I20" t="n">
+        <v>464732</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="K20" t="n">
+        <v>36.873046875</v>
+      </c>
+      <c r="L20" t="n">
+        <v>439303</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8482.7080078125</v>
+      </c>
+      <c r="O20" t="n">
+        <v>452814</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.282958984375</v>
+      </c>
+      <c r="R20" t="n">
+        <v>452814</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="T20" t="n">
+        <v>10600.8427734375</v>
+      </c>
+      <c r="U20" t="n">
+        <v>452814</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1x2x10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2x10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1x2x10 : 2x10</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>198.659912109375</v>
+      </c>
+      <c r="F21" t="n">
+        <v>433487</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5126953125</v>
+      </c>
+      <c r="I21" t="n">
+        <v>446502</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>13.9580078125</v>
+      </c>
+      <c r="L21" t="n">
+        <v>442363</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8527.337890625</v>
+      </c>
+      <c r="O21" t="n">
+        <v>451715</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.218994140625</v>
+      </c>
+      <c r="R21" t="n">
+        <v>451715</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>10743.68676757812</v>
+      </c>
+      <c r="U21" t="n">
+        <v>451715</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48.170166015625</v>
+      </c>
+      <c r="F22" t="n">
+        <v>238698</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.18017578125</v>
+      </c>
+      <c r="I22" t="n">
+        <v>253675</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.951171875</v>
+      </c>
+      <c r="L22" t="n">
+        <v>246986</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3002.194091796875</v>
+      </c>
+      <c r="O22" t="n">
+        <v>259471</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.479248046875</v>
+      </c>
+      <c r="R22" t="n">
+        <v>259471</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2332.253173828125</v>
+      </c>
+      <c r="U22" t="n">
+        <v>259471</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>47.481201171875</v>
+      </c>
+      <c r="F23" t="n">
+        <v>226962</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.18896484375</v>
+      </c>
+      <c r="I23" t="n">
+        <v>235808</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.658935546875</v>
+      </c>
+      <c r="L23" t="n">
+        <v>227738</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3052.229248046875</v>
+      </c>
+      <c r="O23" t="n">
+        <v>241132</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.495849609375</v>
+      </c>
+      <c r="R23" t="n">
+        <v>241132</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2343.873046875</v>
+      </c>
+      <c r="U23" t="n">
+        <v>241132</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>125.672119140625</v>
+      </c>
+      <c r="F24" t="n">
+        <v>235029</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.18408203125</v>
+      </c>
+      <c r="I24" t="n">
+        <v>243180</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.2802734375</v>
+      </c>
+      <c r="L24" t="n">
+        <v>238126</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3005.696044921875</v>
+      </c>
+      <c r="O24" t="n">
+        <v>243180</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.5517578125</v>
+      </c>
+      <c r="R24" t="n">
+        <v>243180</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2346.7568359375</v>
+      </c>
+      <c r="U24" t="n">
+        <v>243180</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>65.598876953125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>230743</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.186767578125</v>
+      </c>
+      <c r="I25" t="n">
+        <v>244134</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6.323974609375</v>
+      </c>
+      <c r="L25" t="n">
+        <v>232731</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3264.43505859375</v>
+      </c>
+      <c r="O25" t="n">
+        <v>244706</v>
+      </c>
+      <c r="P25" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.55078125</v>
+      </c>
+      <c r="R25" t="n">
+        <v>244706</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2339.994140625</v>
+      </c>
+      <c r="U25" t="n">
+        <v>244706</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>68.005126953125</v>
+      </c>
+      <c r="F26" t="n">
+        <v>237497</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.18701171875</v>
+      </c>
+      <c r="I26" t="n">
+        <v>250750</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.9541015625</v>
+      </c>
+      <c r="L26" t="n">
+        <v>238986</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3027.083984375</v>
+      </c>
+      <c r="O26" t="n">
+        <v>250750</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.549072265625</v>
+      </c>
+      <c r="R26" t="n">
+        <v>250750</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2352.02587890625</v>
+      </c>
+      <c r="U26" t="n">
+        <v>250750</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>67.410888671875</v>
+      </c>
+      <c r="F27" t="n">
+        <v>229708</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.18115234375</v>
+      </c>
+      <c r="I27" t="n">
+        <v>235344</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.845947265625</v>
+      </c>
+      <c r="L27" t="n">
+        <v>229961</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3010.961181640625</v>
+      </c>
+      <c r="O27" t="n">
+        <v>235344</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.482177734375</v>
+      </c>
+      <c r="R27" t="n">
+        <v>235344</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2345.351318359375</v>
+      </c>
+      <c r="U27" t="n">
+        <v>235344</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>276.48291015625</v>
+      </c>
+      <c r="F28" t="n">
+        <v>240328</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.187255859375</v>
+      </c>
+      <c r="I28" t="n">
+        <v>250810</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K28" t="n">
+        <v>9.521240234375</v>
+      </c>
+      <c r="L28" t="n">
+        <v>240328</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3124.100830078125</v>
+      </c>
+      <c r="O28" t="n">
+        <v>250810</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.68115234375</v>
+      </c>
+      <c r="R28" t="n">
+        <v>250810</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2344.3662109375</v>
+      </c>
+      <c r="U28" t="n">
+        <v>250810</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>48.883056640625</v>
+      </c>
+      <c r="F29" t="n">
+        <v>232731</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.189208984375</v>
+      </c>
+      <c r="I29" t="n">
+        <v>242983</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.951904296875</v>
+      </c>
+      <c r="L29" t="n">
+        <v>235263</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3017.31298828125</v>
+      </c>
+      <c r="O29" t="n">
+        <v>242983</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.5380859375</v>
+      </c>
+      <c r="R29" t="n">
+        <v>242983</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2343.779052734375</v>
+      </c>
+      <c r="U29" t="n">
+        <v>242983</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>125.88720703125</v>
+      </c>
+      <c r="F30" t="n">
+        <v>243354</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.187744140625</v>
+      </c>
+      <c r="I30" t="n">
+        <v>258318</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.872802734375</v>
+      </c>
+      <c r="L30" t="n">
+        <v>243561</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3030.552978515625</v>
+      </c>
+      <c r="O30" t="n">
+        <v>258318</v>
+      </c>
+      <c r="P30" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.618896484375</v>
+      </c>
+      <c r="R30" t="n">
+        <v>258318</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2338.057861328125</v>
+      </c>
+      <c r="U30" t="n">
+        <v>258318</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1x2x5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2x5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1x2x5 : 2x5</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
         <v>103.207763671875</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F31" t="n">
         <v>233632</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.186767578125</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I31" t="n">
         <v>243221</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J31" t="n">
         <v>4.1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K31" t="n">
         <v>8.660888671875</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L31" t="n">
         <v>233632</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>3007.3720703125</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O31" t="n">
         <v>243221</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P31" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q31" t="n">
         <v>1.5126953125</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R31" t="n">
         <v>243221</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S31" t="n">
         <v>4.1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T31" t="n">
         <v>2335.2998046875</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U31" t="n">
         <v>243221</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V31" t="n">
         <v>4.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4773.2607421875</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1440359</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.173095703125</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1477584</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2428.44580078125</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1448891</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N32" t="n">
+        <v>67094.65698242188</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1492490</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>25.1259765625</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1492490</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T32" t="n">
+        <v>143744.0458984375</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1492490</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4524.65673828125</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1439374</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6.8291015625</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1486840</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3494.59326171875</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1455170</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>66796.67797851562</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1488164</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>24.716796875</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1488164</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T33" t="n">
+        <v>142439.9858398438</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1488164</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4143.19580078125</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1435030</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.214111328125</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1472200</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2023.769775390625</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1447826</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N34" t="n">
+        <v>67236.19067382812</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1476259</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>24.666015625</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1476259</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T34" t="n">
+        <v>143664.0139160156</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1476259</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7000.331787109375</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1442123</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6.900146484375</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1488823</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2698.37890625</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1455574</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N35" t="n">
+        <v>67090.54125976562</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1493865</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>25.27392578125</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1493865</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T35" t="n">
+        <v>143986.5598144531</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1493865</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6452.65185546875</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1441465</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.205078125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1489981</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2836.744384765625</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1454472</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N36" t="n">
+        <v>67331.97021484375</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1477717</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>24.6640625</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1477717</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T36" t="n">
+        <v>143242.3181152344</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1477717</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12162.833984375</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1435658</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.17529296875</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1485571</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2284.6240234375</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1447561</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N37" t="n">
+        <v>67193.52294921875</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1470948</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>24.307861328125</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1470948</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T37" t="n">
+        <v>144463.8369140625</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1470948</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4448.201904296875</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1441442</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.259033203125</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1481281</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2783.50830078125</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1453006</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>66859.5791015625</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1481250</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>24.555908203125</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1481250</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T38" t="n">
+        <v>144418.0048828125</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1481250</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10209.18725585938</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1435590</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.121826171875</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1492934</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2972.318115234375</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1447905</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N39" t="n">
+        <v>67231.69604492188</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1483593</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>24.26806640625</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1483593</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T39" t="n">
+        <v>144176.8933105469</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1483593</v>
+      </c>
+      <c r="V39" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5161.94482421875</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1446920</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7.192138671875</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1480789</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1760.908935546875</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1463025</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N40" t="n">
+        <v>67279.77978515625</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1495850</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>24.965087890625</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1495850</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T40" t="n">
+        <v>144013.5141601562</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1495850</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1x2x35</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2x35</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1x2x35 : 2x35</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5981.5771484375</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1440116</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.14306640625</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1493423</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2957.2490234375</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1453708</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N41" t="n">
+        <v>66871.91821289062</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1497519</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>24.876708984375</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1497519</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="T41" t="n">
+        <v>143713.2380371094</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1497519</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1606.14404296875</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1031069</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.209716796875</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1076119</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K42" t="n">
+        <v>668.837890625</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1044999</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N42" t="n">
+        <v>36251.71313476562</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1076076</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>13.19091796875</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1076076</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="T42" t="n">
+        <v>72349.99682617188</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1076076</v>
+      </c>
+      <c r="V42" t="n">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2156.76904296875</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1037369</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.240966796875</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1074983</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K43" t="n">
+        <v>945.35205078125</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1048605</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N43" t="n">
+        <v>36758.16796875</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1077838</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>13.519775390625</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1077838</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T43" t="n">
+        <v>72625.87890625</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1077838</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>7087.4658203125</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1042807</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.31494140625</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1074739</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1049.31201171875</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1052901</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N44" t="n">
+        <v>36337.34741210938</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1070475</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>13.1611328125</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1070475</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T44" t="n">
+        <v>71830.59887695312</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1070475</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1489.956787109375</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1032348</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.287841796875</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1052539</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>536.451904296875</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1038261</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N45" t="n">
+        <v>36225.2509765625</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1057823</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>13.487060546875</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1057823</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T45" t="n">
+        <v>71767.10791015625</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1057823</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2675.39892578125</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1036427</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.184814453125</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1072435</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K46" t="n">
+        <v>737.169921875</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1046522</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N46" t="n">
+        <v>36300.51147460938</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1065718</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>13.4521484375</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1065718</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T46" t="n">
+        <v>72394.49291992188</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1065718</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1614.823486328125</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1039625</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.30712890625</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1069131</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K47" t="n">
+        <v>572.990966796875</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1048375</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N47" t="n">
+        <v>36671.47241210938</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1085445</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>13.513916015625</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1085445</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="T47" t="n">
+        <v>71816.92211914062</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1085445</v>
+      </c>
+      <c r="V47" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2766.788330078125</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1038409</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.338134765625</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1084654</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1489.915771484375</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1049144</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N48" t="n">
+        <v>36265.46411132812</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1087465</v>
+      </c>
+      <c r="P48" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>13.8759765625</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1087465</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="T48" t="n">
+        <v>72367.02392578125</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1087465</v>
+      </c>
+      <c r="V48" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1836.03173828125</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1038051</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.28564453125</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1082106</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="K49" t="n">
+        <v>842.044921875</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1050359</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N49" t="n">
+        <v>36346.48583984375</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1075565</v>
+      </c>
+      <c r="P49" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>13.516845703125</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1075565</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="T49" t="n">
+        <v>72211.18798828125</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1075565</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2559.66796875</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1038570</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.194091796875</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1068624</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K50" t="n">
+        <v>785.602783203125</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1046798</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N50" t="n">
+        <v>36204.7841796875</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1067568</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>13.47314453125</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1067568</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T50" t="n">
+        <v>71993.23681640625</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1067568</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1x2x25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2x25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1x2x25 : 2x25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2180.90625</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1037890</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.22412109375</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1084266</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1462.57421875</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1046492</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N51" t="n">
+        <v>36644.90991210938</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1076901</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>13.162841796875</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1076901</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T51" t="n">
+        <v>71851.23022460938</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1076901</v>
+      </c>
+      <c r="V51" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1006.92626953125</v>
+      </c>
+      <c r="F52" t="n">
+        <v>837669</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.546875</v>
+      </c>
+      <c r="I52" t="n">
+        <v>865115</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="K52" t="n">
+        <v>312.888671875</v>
+      </c>
+      <c r="L52" t="n">
+        <v>846957</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N52" t="n">
+        <v>25647.2177734375</v>
+      </c>
+      <c r="O52" t="n">
+        <v>874417</v>
+      </c>
+      <c r="P52" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>9.298828125</v>
+      </c>
+      <c r="R52" t="n">
+        <v>874417</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="T52" t="n">
+        <v>45812.90600585938</v>
+      </c>
+      <c r="U52" t="n">
+        <v>874417</v>
+      </c>
+      <c r="V52" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1319.021728515625</v>
+      </c>
+      <c r="F53" t="n">
+        <v>848374</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.561279296875</v>
+      </c>
+      <c r="I53" t="n">
+        <v>882392</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="K53" t="n">
+        <v>601.644775390625</v>
+      </c>
+      <c r="L53" t="n">
+        <v>858699</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N53" t="n">
+        <v>25841.30102539062</v>
+      </c>
+      <c r="O53" t="n">
+        <v>879570</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>9.17041015625</v>
+      </c>
+      <c r="R53" t="n">
+        <v>879570</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T53" t="n">
+        <v>45584.21801757812</v>
+      </c>
+      <c r="U53" t="n">
+        <v>879570</v>
+      </c>
+      <c r="V53" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1156.10400390625</v>
+      </c>
+      <c r="F54" t="n">
+        <v>836918</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.66796875</v>
+      </c>
+      <c r="I54" t="n">
+        <v>863735</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K54" t="n">
+        <v>216.1005859375</v>
+      </c>
+      <c r="L54" t="n">
+        <v>845313</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>25657.27514648437</v>
+      </c>
+      <c r="O54" t="n">
+        <v>872623</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>9.72314453125</v>
+      </c>
+      <c r="R54" t="n">
+        <v>872623</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="T54" t="n">
+        <v>45724.46020507812</v>
+      </c>
+      <c r="U54" t="n">
+        <v>872623</v>
+      </c>
+      <c r="V54" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1008.360107421875</v>
+      </c>
+      <c r="F55" t="n">
+        <v>839932</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.587890625</v>
+      </c>
+      <c r="I55" t="n">
+        <v>869092</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K55" t="n">
+        <v>289.044189453125</v>
+      </c>
+      <c r="L55" t="n">
+        <v>849175</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>25573.77587890625</v>
+      </c>
+      <c r="O55" t="n">
+        <v>865358</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>9.363037109375</v>
+      </c>
+      <c r="R55" t="n">
+        <v>865358</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T55" t="n">
+        <v>45931.86889648438</v>
+      </c>
+      <c r="U55" t="n">
+        <v>865358</v>
+      </c>
+      <c r="V55" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="n">
+        <v>888.93603515625</v>
+      </c>
+      <c r="F56" t="n">
+        <v>836312</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.52001953125</v>
+      </c>
+      <c r="I56" t="n">
+        <v>872844</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K56" t="n">
+        <v>340.63623046875</v>
+      </c>
+      <c r="L56" t="n">
+        <v>845274</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N56" t="n">
+        <v>25714.67504882812</v>
+      </c>
+      <c r="O56" t="n">
+        <v>864605</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>9.344970703125</v>
+      </c>
+      <c r="R56" t="n">
+        <v>864605</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T56" t="n">
+        <v>45472.73291015625</v>
+      </c>
+      <c r="U56" t="n">
+        <v>864605</v>
+      </c>
+      <c r="V56" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1023.96484375</v>
+      </c>
+      <c r="F57" t="n">
+        <v>841242</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.548095703125</v>
+      </c>
+      <c r="I57" t="n">
+        <v>877872</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="K57" t="n">
+        <v>618.662109375</v>
+      </c>
+      <c r="L57" t="n">
+        <v>850175</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N57" t="n">
+        <v>25813.56176757812</v>
+      </c>
+      <c r="O57" t="n">
+        <v>863421</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>9.28466796875</v>
+      </c>
+      <c r="R57" t="n">
+        <v>863421</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T57" t="n">
+        <v>45819.86889648438</v>
+      </c>
+      <c r="U57" t="n">
+        <v>863421</v>
+      </c>
+      <c r="V57" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1037.848876953125</v>
+      </c>
+      <c r="F58" t="n">
+        <v>838025</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.59423828125</v>
+      </c>
+      <c r="I58" t="n">
+        <v>863577</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K58" t="n">
+        <v>287.9169921875</v>
+      </c>
+      <c r="L58" t="n">
+        <v>851504</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25796.63500976562</v>
+      </c>
+      <c r="O58" t="n">
+        <v>870330</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>10.260009765625</v>
+      </c>
+      <c r="R58" t="n">
+        <v>870330</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T58" t="n">
+        <v>46105.80297851562</v>
+      </c>
+      <c r="U58" t="n">
+        <v>870330</v>
+      </c>
+      <c r="V58" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1305.27880859375</v>
+      </c>
+      <c r="F59" t="n">
+        <v>838710</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.5419921875</v>
+      </c>
+      <c r="I59" t="n">
+        <v>859526</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K59" t="n">
+        <v>370.128173828125</v>
+      </c>
+      <c r="L59" t="n">
+        <v>843369</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N59" t="n">
+        <v>25687.412109375</v>
+      </c>
+      <c r="O59" t="n">
+        <v>875814</v>
+      </c>
+      <c r="P59" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>9.22509765625</v>
+      </c>
+      <c r="R59" t="n">
+        <v>875814</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="T59" t="n">
+        <v>45769.28295898438</v>
+      </c>
+      <c r="U59" t="n">
+        <v>875814</v>
+      </c>
+      <c r="V59" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>9</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2482.241943359375</v>
+      </c>
+      <c r="F60" t="n">
+        <v>836637</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.503173828125</v>
+      </c>
+      <c r="I60" t="n">
+        <v>870117</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" t="n">
+        <v>506.125</v>
+      </c>
+      <c r="L60" t="n">
+        <v>845849</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>25830.29028320312</v>
+      </c>
+      <c r="O60" t="n">
+        <v>877701</v>
+      </c>
+      <c r="P60" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>9.331298828125</v>
+      </c>
+      <c r="R60" t="n">
+        <v>877701</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="T60" t="n">
+        <v>45632.0869140625</v>
+      </c>
+      <c r="U60" t="n">
+        <v>877701</v>
+      </c>
+      <c r="V60" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1x2x20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1x2x20 : 2x20</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2054.35986328125</v>
+      </c>
+      <c r="F61" t="n">
+        <v>841055</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.552978515625</v>
+      </c>
+      <c r="I61" t="n">
+        <v>870153</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="K61" t="n">
+        <v>365.498291015625</v>
+      </c>
+      <c r="L61" t="n">
+        <v>846399</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N61" t="n">
+        <v>25938.56103515625</v>
+      </c>
+      <c r="O61" t="n">
+        <v>868028</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>9.5107421875</v>
+      </c>
+      <c r="R61" t="n">
+        <v>868028</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="T61" t="n">
+        <v>45732.11962890625</v>
+      </c>
+      <c r="U61" t="n">
+        <v>868028</v>
+      </c>
+      <c r="V61" t="n">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>17775.673828125</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2042593</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9.2880859375</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2083280</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="K62" t="n">
+        <v>8131.994140625</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2059450</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N62" t="n">
+        <v>128719.3000488281</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2073897</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>47.8740234375</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2073897</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T62" t="n">
+        <v>296647.0522460937</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2073897</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>15424.1513671875</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2045670</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>9.008056640625</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2096232</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K63" t="n">
+        <v>10003.70581054688</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2063804</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N63" t="n">
+        <v>129083.9431152344</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2092464</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>47.43115234375</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2092464</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T63" t="n">
+        <v>295107.546875</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2092464</v>
+      </c>
+      <c r="V63" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>28156.47827148437</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2038492</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>9.2861328125</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2087963</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K64" t="n">
+        <v>14385.76806640625</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2055045</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N64" t="n">
+        <v>128304.4348144531</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2088044</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>46.811767578125</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2088044</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T64" t="n">
+        <v>296086.7429199219</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2088044</v>
+      </c>
+      <c r="V64" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>15732.3046875</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2037734</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>8.8642578125</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2100560</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K65" t="n">
+        <v>12947.51684570312</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2053727</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N65" t="n">
+        <v>128427.7438964844</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2090016</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>47.901123046875</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2090016</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T65" t="n">
+        <v>294881.0551757812</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2090016</v>
+      </c>
+      <c r="V65" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="n">
+        <v>12301.966796875</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2035758</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>8.642578125</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2091236</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K66" t="n">
+        <v>12220.26831054688</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2053299</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N66" t="n">
+        <v>128752.2021484375</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2096202</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>48.2900390625</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2096202</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T66" t="n">
+        <v>295112.2329101562</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2096202</v>
+      </c>
+      <c r="V66" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="n">
+        <v>26530.7958984375</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2039698</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>9.549072265625</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2084405</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K67" t="n">
+        <v>9231.75390625</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2056822</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N67" t="n">
+        <v>128653.9077148438</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2085832</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>48.114990234375</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2085832</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T67" t="n">
+        <v>295138.2333984375</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2085832</v>
+      </c>
+      <c r="V67" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>27232.9892578125</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2038924</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8.042236328125</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2089177</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K68" t="n">
+        <v>11558.62109375</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2051527</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N68" t="n">
+        <v>127825.9382324219</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2093470</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>47.48779296875</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2093470</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T68" t="n">
+        <v>295004.66796875</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2093470</v>
+      </c>
+      <c r="V68" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" t="n">
+        <v>14233.69091796875</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2043445</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>9.038818359375</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2080176</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K69" t="n">
+        <v>10718.40405273438</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2058499</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N69" t="n">
+        <v>128867.7829589844</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2095709</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>48.572265625</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2095709</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T69" t="n">
+        <v>294180.671875</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2095709</v>
+      </c>
+      <c r="V69" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>11555.59692382812</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2044168</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>9.30810546875</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2095900</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K70" t="n">
+        <v>8464.857177734375</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2063949</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N70" t="n">
+        <v>128714.6450195312</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2112240</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>48.568603515625</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2112240</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T70" t="n">
+        <v>296411.8977050781</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2112240</v>
+      </c>
+      <c r="V70" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1x2x50</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2x50</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1x2x50 : 2x50</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="n">
+        <v>13761.26171875</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2039182</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>9.304931640625</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2098726</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K71" t="n">
+        <v>11059.07592773438</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2057610</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N71" t="n">
+        <v>128902.8430175781</v>
+      </c>
+      <c r="O71" t="n">
+        <v>2101395</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>47.480224609375</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2101395</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T71" t="n">
+        <v>298028.6220703125</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2101395</v>
+      </c>
+      <c r="V71" t="n">
+        <v>3.05</v>
       </c>
     </row>
   </sheetData>
